--- a/tests/samples/phone_formats.xlsx
+++ b/tests/samples/phone_formats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\contacts manager\tests\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B56B9FDB-22E0-4629-BCD3-4997F7098492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E30C4E71-A2F3-4CB0-B4E8-DC1D6C1C6066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{5B19CE1F-350B-4874-BA95-4E89F4A383AD}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{24FF73DF-93CE-4062-BCE8-CFBBE8FD87DB}"/>
   </bookViews>
   <sheets>
     <sheet name="الأرقام" sheetId="1" r:id="rId1"/>
@@ -451,7 +451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1ECC0FA-FB6A-4DAA-80BF-E28D525D8941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9ABE6A3-A532-45E1-A8AC-3AC0DD6C7B94}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
